--- a/artfynd/A 32339-2026 artfynd.xlsx
+++ b/artfynd/A 32339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745099</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744058</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135744570</v>
       </c>
       <c r="B31" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135744735</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135744785</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135744856</v>
       </c>
       <c r="B34" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135745169</v>
       </c>
       <c r="B35" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 32339-2026 artfynd.xlsx
+++ b/artfynd/A 32339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745099</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135744229</v>
       </c>
       <c r="B3" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744058</v>
       </c>
       <c r="B4" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743935</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135744106</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135744189</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135744264</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135744688</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135744805</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135744808</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135745071</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135745097</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135744740</v>
       </c>
       <c r="B14" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135743975</v>
       </c>
       <c r="B15" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135744212</v>
       </c>
       <c r="B16" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135744372</v>
       </c>
       <c r="B17" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135744394</v>
       </c>
       <c r="B18" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135744516</v>
       </c>
       <c r="B19" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135744534</v>
       </c>
       <c r="B20" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135744751</v>
       </c>
       <c r="B21" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135744999</v>
       </c>
       <c r="B22" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135745065</v>
       </c>
       <c r="B23" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135745229</v>
       </c>
       <c r="B24" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135745400</v>
       </c>
       <c r="B25" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135745519</v>
       </c>
       <c r="B26" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135744594</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>135744716</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>135744887</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135744345</v>
       </c>
       <c r="B30" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135744570</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135744735</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135744785</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135744856</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135745169</v>
       </c>
       <c r="B35" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 32339-2026 artfynd.xlsx
+++ b/artfynd/A 32339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745099</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135744229</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744058</v>
       </c>
       <c r="B4" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743935</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135744106</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135744189</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135744264</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135744688</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135744805</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135744808</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135745071</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135745097</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135744740</v>
       </c>
       <c r="B14" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135743975</v>
       </c>
       <c r="B15" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135744212</v>
       </c>
       <c r="B16" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135744372</v>
       </c>
       <c r="B17" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135744394</v>
       </c>
       <c r="B18" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135744516</v>
       </c>
       <c r="B19" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135744534</v>
       </c>
       <c r="B20" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135744751</v>
       </c>
       <c r="B21" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135744999</v>
       </c>
       <c r="B22" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135745065</v>
       </c>
       <c r="B23" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135745229</v>
       </c>
       <c r="B24" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135745400</v>
       </c>
       <c r="B25" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135745519</v>
       </c>
       <c r="B26" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135744570</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135744735</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135744785</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135744856</v>
       </c>
       <c r="B34" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135745169</v>
       </c>
       <c r="B35" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 32339-2026 artfynd.xlsx
+++ b/artfynd/A 32339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745099</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744058</v>
       </c>
       <c r="B4" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135744570</v>
       </c>
       <c r="B31" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135744735</v>
       </c>
       <c r="B32" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135744785</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135744856</v>
       </c>
       <c r="B34" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135745169</v>
       </c>
       <c r="B35" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 32339-2026 artfynd.xlsx
+++ b/artfynd/A 32339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745099</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135744229</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744058</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743935</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135744106</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135744189</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135744264</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135744688</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135744805</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135744808</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135745071</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135745097</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135744740</v>
       </c>
       <c r="B14" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135743975</v>
       </c>
       <c r="B15" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135744212</v>
       </c>
       <c r="B16" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135744372</v>
       </c>
       <c r="B17" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135744394</v>
       </c>
       <c r="B18" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135744516</v>
       </c>
       <c r="B19" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135744534</v>
       </c>
       <c r="B20" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135744751</v>
       </c>
       <c r="B21" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135744999</v>
       </c>
       <c r="B22" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135745065</v>
       </c>
       <c r="B23" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135745229</v>
       </c>
       <c r="B24" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135745400</v>
       </c>
       <c r="B25" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135745519</v>
       </c>
       <c r="B26" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135744594</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>135744716</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>135744887</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135744345</v>
       </c>
       <c r="B30" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135744570</v>
       </c>
       <c r="B31" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135744735</v>
       </c>
       <c r="B32" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135744785</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135744856</v>
       </c>
       <c r="B34" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135745169</v>
       </c>
       <c r="B35" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 32339-2026 artfynd.xlsx
+++ b/artfynd/A 32339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745099</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135744229</v>
       </c>
       <c r="B3" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744058</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743935</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135744106</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135744189</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135744264</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135744688</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135744805</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135744808</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135745071</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135745097</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135744740</v>
       </c>
       <c r="B14" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135743975</v>
       </c>
       <c r="B15" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135744212</v>
       </c>
       <c r="B16" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135744372</v>
       </c>
       <c r="B17" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135744394</v>
       </c>
       <c r="B18" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135744516</v>
       </c>
       <c r="B19" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135744534</v>
       </c>
       <c r="B20" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135744751</v>
       </c>
       <c r="B21" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135744999</v>
       </c>
       <c r="B22" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135745065</v>
       </c>
       <c r="B23" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135745229</v>
       </c>
       <c r="B24" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135745400</v>
       </c>
       <c r="B25" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135745519</v>
       </c>
       <c r="B26" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135744594</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>135744716</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>135744887</v>
       </c>
       <c r="B29" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135744345</v>
       </c>
       <c r="B30" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135744570</v>
       </c>
       <c r="B31" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135744735</v>
       </c>
       <c r="B32" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135744785</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135744856</v>
       </c>
       <c r="B34" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135745169</v>
       </c>
       <c r="B35" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 32339-2026 artfynd.xlsx
+++ b/artfynd/A 32339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745099</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135744229</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744058</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743935</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135744106</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135744189</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135744264</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135744688</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135744805</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135744808</v>
       </c>
       <c r="B11" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135745071</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135745097</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135744740</v>
       </c>
       <c r="B14" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135743975</v>
       </c>
       <c r="B15" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135744212</v>
       </c>
       <c r="B16" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135744372</v>
       </c>
       <c r="B17" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135744394</v>
       </c>
       <c r="B18" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135744516</v>
       </c>
       <c r="B19" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135744534</v>
       </c>
       <c r="B20" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135744751</v>
       </c>
       <c r="B21" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135744999</v>
       </c>
       <c r="B22" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135745065</v>
       </c>
       <c r="B23" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135745229</v>
       </c>
       <c r="B24" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135745400</v>
       </c>
       <c r="B25" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135745519</v>
       </c>
       <c r="B26" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135744594</v>
       </c>
       <c r="B27" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>135744716</v>
       </c>
       <c r="B28" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>135744887</v>
       </c>
       <c r="B29" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135744345</v>
       </c>
       <c r="B30" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135744570</v>
       </c>
       <c r="B31" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135744735</v>
       </c>
       <c r="B32" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135744785</v>
       </c>
       <c r="B33" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135744856</v>
       </c>
       <c r="B34" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135745169</v>
       </c>
       <c r="B35" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 32339-2026 artfynd.xlsx
+++ b/artfynd/A 32339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745099</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135744229</v>
       </c>
       <c r="B3" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744058</v>
       </c>
       <c r="B4" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743935</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135744106</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135744189</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135744264</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135744688</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135744805</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135744808</v>
       </c>
       <c r="B11" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135745071</v>
       </c>
       <c r="B12" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135745097</v>
       </c>
       <c r="B13" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135744740</v>
       </c>
       <c r="B14" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135743975</v>
       </c>
       <c r="B15" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135744212</v>
       </c>
       <c r="B16" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135744372</v>
       </c>
       <c r="B17" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135744394</v>
       </c>
       <c r="B18" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135744516</v>
       </c>
       <c r="B19" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135744534</v>
       </c>
       <c r="B20" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135744751</v>
       </c>
       <c r="B21" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135744999</v>
       </c>
       <c r="B22" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135745065</v>
       </c>
       <c r="B23" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135745229</v>
       </c>
       <c r="B24" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135745400</v>
       </c>
       <c r="B25" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135745519</v>
       </c>
       <c r="B26" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135744570</v>
       </c>
       <c r="B31" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135744735</v>
       </c>
       <c r="B32" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135744785</v>
       </c>
       <c r="B33" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135744856</v>
       </c>
       <c r="B34" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135745169</v>
       </c>
       <c r="B35" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 32339-2026 artfynd.xlsx
+++ b/artfynd/A 32339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135745099</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135744229</v>
       </c>
       <c r="B3" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744058</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135743935</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135744106</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135744189</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135744264</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135744688</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>135744805</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>135744808</v>
       </c>
       <c r="B11" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135745071</v>
       </c>
       <c r="B12" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>135745097</v>
       </c>
       <c r="B13" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>135744740</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>135743975</v>
       </c>
       <c r="B15" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>135744212</v>
       </c>
       <c r="B16" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>135744372</v>
       </c>
       <c r="B17" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>135744394</v>
       </c>
       <c r="B18" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>135744516</v>
       </c>
       <c r="B19" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135744534</v>
       </c>
       <c r="B20" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135744751</v>
       </c>
       <c r="B21" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>135744999</v>
       </c>
       <c r="B22" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>135745065</v>
       </c>
       <c r="B23" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>135745229</v>
       </c>
       <c r="B24" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>135745400</v>
       </c>
       <c r="B25" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135745519</v>
       </c>
       <c r="B26" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>135744594</v>
       </c>
       <c r="B27" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>135744716</v>
       </c>
       <c r="B28" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>135744887</v>
       </c>
       <c r="B29" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135744345</v>
       </c>
       <c r="B30" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135744570</v>
       </c>
       <c r="B31" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135744735</v>
       </c>
       <c r="B32" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135744785</v>
       </c>
       <c r="B33" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135744856</v>
       </c>
       <c r="B34" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135745169</v>
       </c>
       <c r="B35" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
